--- a/site/exports/nwsuaf-cie-data.xlsx
+++ b/site/exports/nwsuaf-cie-data.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R66b28607c57d4f1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R8b5ab55be8184807"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="Rdd3780db8a534818"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R6acc6db998324926"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R5e0bcee6ebeb405f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf2e588dd07a7459b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="Rf5c2fa6170ce4954"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="Rec5e2c3832024eab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R2a4903d4486b443a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R504e6af29493422d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T31_0" displayName="T31_0" ref="A1:K2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T59_0" displayName="T59_0" ref="A1:K2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="校区"/>
@@ -111,7 +111,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T31_1" displayName="T31_1" ref="A1:S4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T59_1" displayName="T59_1" ref="A1:S4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="事件类型"/>
@@ -138,7 +138,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T31_4" displayName="T31_4" ref="A1:G3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T59_4" displayName="T59_4" ref="A1:G3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="来源ID"/>
@@ -353,7 +353,7 @@
     <x:col min="4" max="4" width="26" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="55" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="55" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="110" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="26" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="26" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="26" hidden="0" customWidth="1"/>
@@ -395,7 +395,7 @@
         <x:v>所属学校</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="64" customHeight="1">
+    <x:row r="2" ht="150" customHeight="1">
       <x:c r="A2" s="6" t="str">
         <x:v>李书琴</x:v>
       </x:c>
@@ -415,7 +415,7 @@
         <x:v>未核得本人导师，不由合著或指导学生名单推断。；精选书目非全集，无逐篇链接时只列官网书目。；未披露本人学历或逐篇论文，不由博士生导师头衔推断本人博士学位。</x:v>
       </x:c>
       <x:c r="G2" s="6" t="str">
-        <x:v>分批核实资料，不是完整名录</x:v>
+        <x:v>分批核实资料，不是完整名录；部分职业履历，学历与师承仍有缺项；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：数据库原理与应用、数据科学与技术导论；角色未披露；教学／课程开设时间：时间未披露；来源ID：lishuqin-source-2；https://cie.nwsuaf.edu.cn/szdw/js/2008115466/index.htm</x:v>
       </x:c>
       <x:c r="H2" s="6" t="str">
         <x:v>公开个人页（时效以核对日为准）</x:v>
@@ -431,7 +431,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf6160a306d74d5c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R528372e540824ae0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -636,7 +636,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31cd2444bebe4a8b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb587d9568743479d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -848,7 +848,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R144e1680672e4b78"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e4284f763fd4960"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/exports/nwsuaf-cie-data.xlsx
+++ b/site/exports/nwsuaf-cie-data.xlsx
@@ -453,7 +453,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="26.6" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -482,7 +482,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>核对日期</t>
+          <t>已记录来源检索日期</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录；部分职业履历，学历与师承仍有缺项；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：数据库原理与应用、数据科学与技术导论；角色未披露；教学／课程开设时间：时间未披露；来源ID：lishuqin-source-2；https://cie.nwsuaf.edu.cn/szdw/js/2008115466/index.htm</t>
+          <t>分批核实资料，不是完整名录；部分职业履历，学历与师承仍有缺项；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：数据库原理与应用、数据科学与技术导论；角色未披露；教学／课程开设时间：时间未披露；来源ID：lishuqin-source-2；https://cie.nwsuaf.edu.cn/szdw/js/2008115466/index.htm；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
